--- a/exports/trend_1d/AMBER_full_report.xlsx
+++ b/exports/trend_1d/AMBER_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:U51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>18.57</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>43251</v>
+        <v>43252</v>
       </c>
       <c r="H2" t="n">
-        <v>1080.15</v>
+        <v>1069.4</v>
       </c>
       <c r="I2" t="n">
         <v>1077.661584220818</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K2" t="n">
-        <v>-8.92</v>
+        <v>-9.83</v>
       </c>
       <c r="L2" t="n">
         <v>10.97</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>10.47</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43283</v>
+        <v>43284</v>
       </c>
       <c r="H3" t="n">
-        <v>897.5</v>
+        <v>1020.25</v>
       </c>
       <c r="I3" t="n">
         <v>998.1659179440774</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K3" t="n">
-        <v>16.07</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
         <v>2.02</v>
@@ -612,7 +647,7 @@
         <v>3.18</v>
       </c>
       <c r="N3" t="n">
-        <v>3.29</v>
+        <v>13.68</v>
       </c>
       <c r="O3" t="n">
         <v>-1</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>20.16</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>43378</v>
+        <v>43381</v>
       </c>
       <c r="H4" t="n">
-        <v>897.65</v>
+        <v>885.95</v>
       </c>
       <c r="I4" t="n">
         <v>895.6475251454988</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K4" t="n">
-        <v>-12.02</v>
+        <v>-13.16</v>
       </c>
       <c r="L4" t="n">
-        <v>12.87</v>
+        <v>13.95</v>
       </c>
       <c r="M4" t="n">
         <v>2.27</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>11.74</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>43430</v>
+        <v>43431</v>
       </c>
       <c r="H5" t="n">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="I5" t="n">
         <v>914.9002279488743</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.71</v>
+        <v>-3.28</v>
       </c>
       <c r="L5" t="n">
         <v>6.55</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>8.65</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43488</v>
+        <v>43489</v>
       </c>
       <c r="H6" t="n">
-        <v>860.45</v>
+        <v>845.95</v>
       </c>
       <c r="I6" t="n">
         <v>859.6276722557038</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.96</v>
+        <v>-7.55</v>
       </c>
       <c r="L6" t="n">
-        <v>7.64</v>
+        <v>7.76</v>
       </c>
       <c r="M6" t="n">
         <v>2.88</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>8.35</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43530</v>
+        <v>43531</v>
       </c>
       <c r="H7" t="n">
-        <v>722.75</v>
+        <v>743.95</v>
       </c>
       <c r="I7" t="n">
         <v>723.8468754417294</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K7" t="n">
-        <v>14.56</v>
+        <v>12.06</v>
       </c>
       <c r="L7" t="n">
         <v>2.46</v>
       </c>
       <c r="M7" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="N7" t="n">
         <v>4.03</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>12.39</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43592</v>
+        <v>43593</v>
       </c>
       <c r="H8" t="n">
-        <v>790</v>
+        <v>761.9</v>
       </c>
       <c r="I8" t="n">
         <v>772.5055207518233</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K8" t="n">
-        <v>6.19</v>
+        <v>2.41</v>
       </c>
       <c r="L8" t="n">
         <v>2.55</v>
@@ -897,7 +992,7 @@
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.06</v>
+        <v>3.56</v>
       </c>
       <c r="O8" t="n">
         <v>2.93</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>11.89</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43609</v>
+        <v>43612</v>
       </c>
       <c r="H9" t="n">
-        <v>739.15</v>
+        <v>825.95</v>
       </c>
       <c r="I9" t="n">
         <v>790.4996173317787</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K9" t="n">
-        <v>2.99</v>
+        <v>-8.41</v>
       </c>
       <c r="L9" t="n">
-        <v>3.69</v>
+        <v>14.67</v>
       </c>
       <c r="M9" t="n">
-        <v>2.01</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>3.45</v>
+        <v>11.74</v>
       </c>
       <c r="O9" t="n">
         <v>-3.56</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>11.98</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43679</v>
+        <v>43682</v>
       </c>
       <c r="H10" t="n">
-        <v>783.8</v>
+        <v>763</v>
       </c>
       <c r="I10" t="n">
         <v>780.4423165288247</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.1</v>
+        <v>-7.62</v>
       </c>
       <c r="L10" t="n">
-        <v>7.62</v>
+        <v>9.1</v>
       </c>
       <c r="M10" t="n">
         <v>2.55</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>11.68</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43700</v>
+        <v>43703</v>
       </c>
       <c r="H11" t="n">
-        <v>821.9</v>
+        <v>853.25</v>
       </c>
       <c r="I11" t="n">
         <v>852.1084883802037</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K11" t="n">
-        <v>-7.72</v>
+        <v>-11.83</v>
       </c>
       <c r="L11" t="n">
-        <v>12.71</v>
+        <v>14.03</v>
       </c>
       <c r="M11" t="n">
         <v>2.6</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>12.87</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43887</v>
+        <v>43888</v>
       </c>
       <c r="H12" t="n">
-        <v>1482.85</v>
+        <v>1409.75</v>
       </c>
       <c r="I12" t="n">
         <v>1432.187141041826</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K12" t="n">
-        <v>73.79000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="L12" t="n">
         <v>5.77</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>18.21</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43980</v>
+        <v>43983</v>
       </c>
       <c r="H13" t="n">
-        <v>1245.85</v>
+        <v>1338.55</v>
       </c>
       <c r="I13" t="n">
         <v>1271.061855939332</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K13" t="n">
-        <v>11.63</v>
+        <v>5.05</v>
       </c>
       <c r="L13" t="n">
         <v>6.11</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>15.49</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44279</v>
+        <v>44280</v>
       </c>
       <c r="H14" t="n">
-        <v>3177.35</v>
+        <v>3002.8</v>
       </c>
       <c r="I14" t="n">
         <v>3095.055870107098</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K14" t="n">
-        <v>137.37</v>
+        <v>124.33</v>
       </c>
       <c r="L14" t="n">
         <v>4.52</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>208</v>
+        <v>209</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>10</v>
+      </c>
+      <c r="U14" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -1275,25 +1454,25 @@
         <v>18.87</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44369</v>
+        <v>44370</v>
       </c>
       <c r="H15" t="n">
-        <v>2781.55</v>
+        <v>2910.95</v>
       </c>
       <c r="I15" t="n">
         <v>2907.102482990862</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K15" t="n">
-        <v>7.37</v>
+        <v>3.06</v>
       </c>
       <c r="L15" t="n">
         <v>12.87</v>
       </c>
       <c r="M15" t="n">
-        <v>3.24</v>
+        <v>4.63</v>
       </c>
       <c r="N15" t="n">
         <v>5.65</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,25 +1523,25 @@
         <v>7.8</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44418</v>
+        <v>44419</v>
       </c>
       <c r="H16" t="n">
-        <v>2866.75</v>
+        <v>2835.75</v>
       </c>
       <c r="I16" t="n">
         <v>2843.358766176784</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.52</v>
+        <v>-2.58</v>
       </c>
       <c r="L16" t="n">
-        <v>2.49</v>
+        <v>6.15</v>
       </c>
       <c r="M16" t="n">
-        <v>1.21</v>
+        <v>1.63</v>
       </c>
       <c r="N16" t="n">
         <v>2.93</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>6.05</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44439</v>
+        <v>44440</v>
       </c>
       <c r="H17" t="n">
-        <v>2894.9</v>
+        <v>3027.2</v>
       </c>
       <c r="I17" t="n">
         <v>2976.139355529631</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.09</v>
+        <v>-6.75</v>
       </c>
       <c r="L17" t="n">
-        <v>4.73</v>
+        <v>7.91</v>
       </c>
       <c r="M17" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="N17" t="n">
-        <v>3.11</v>
+        <v>4.57</v>
       </c>
       <c r="O17" t="n">
         <v>-1.08</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>9.41</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44491</v>
+        <v>44494</v>
       </c>
       <c r="H18" t="n">
-        <v>3392.4</v>
+        <v>3222.5</v>
       </c>
       <c r="I18" t="n">
         <v>3279.801934363532</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K18" t="n">
-        <v>12.06</v>
+        <v>6.45</v>
       </c>
       <c r="L18" t="n">
         <v>3.67</v>
@@ -1467,7 +1682,7 @@
         <v>1.34</v>
       </c>
       <c r="N18" t="n">
-        <v>4.83</v>
+        <v>5.01</v>
       </c>
       <c r="O18" t="n">
         <v>4.57</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>17.61</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44572</v>
+        <v>44573</v>
       </c>
       <c r="H19" t="n">
-        <v>3473.8</v>
+        <v>3532.4</v>
       </c>
       <c r="I19" t="n">
         <v>3503.447160151488</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K19" t="n">
-        <v>-7.8</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="L19" t="n">
         <v>11.99</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>10.99</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H20" t="n">
-        <v>3433.95</v>
+        <v>3225.6</v>
       </c>
       <c r="I20" t="n">
         <v>3241.571274986541</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.79</v>
+        <v>-8.69</v>
       </c>
       <c r="L20" t="n">
-        <v>4.49</v>
+        <v>10.54</v>
       </c>
       <c r="M20" t="n">
         <v>1.53</v>
       </c>
       <c r="N20" t="n">
-        <v>4.48</v>
+        <v>6.07</v>
       </c>
       <c r="O20" t="n">
         <v>1.69</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>16.07</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44589</v>
+        <v>44592</v>
       </c>
       <c r="H21" t="n">
-        <v>3190.2</v>
+        <v>3610.05</v>
       </c>
       <c r="I21" t="n">
         <v>3533.670338981331</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1</v>
+        <v>-11.92</v>
       </c>
       <c r="L21" t="n">
-        <v>5.9</v>
+        <v>13.16</v>
       </c>
       <c r="M21" t="n">
-        <v>0.16</v>
+        <v>3.44</v>
       </c>
       <c r="N21" t="n">
-        <v>3.08</v>
+        <v>13.16</v>
       </c>
       <c r="O21" t="n">
         <v>-6.07</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>21.14</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44691</v>
+        <v>44692</v>
       </c>
       <c r="H22" t="n">
-        <v>3470.45</v>
+        <v>3339.65</v>
       </c>
       <c r="I22" t="n">
         <v>3417.114417323143</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.87</v>
+        <v>-7.49</v>
       </c>
       <c r="L22" t="n">
         <v>14.43</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>17.81</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44760</v>
+        <v>44761</v>
       </c>
       <c r="H23" t="n">
-        <v>2444.3</v>
+        <v>2492.6</v>
       </c>
       <c r="I23" t="n">
         <v>2445.218239607123</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K23" t="n">
-        <v>26.81</v>
+        <v>25.36</v>
       </c>
       <c r="L23" t="n">
         <v>4.8</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>12.93</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44781</v>
+        <v>44783</v>
       </c>
       <c r="H24" t="n">
-        <v>2272</v>
+        <v>2184.55</v>
       </c>
       <c r="I24" t="n">
         <v>2266.423653833553</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K24" t="n">
-        <v>-8.85</v>
+        <v>-12.36</v>
       </c>
       <c r="L24" t="n">
-        <v>9.73</v>
+        <v>12.54</v>
       </c>
       <c r="M24" t="n">
         <v>1.3</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>15.76</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44834</v>
+        <v>44837</v>
       </c>
       <c r="H25" t="n">
-        <v>2363.7</v>
+        <v>2372.95</v>
       </c>
       <c r="I25" t="n">
         <v>2365.776185436615</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K25" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>9.44</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="M25" t="n">
         <v>1.34</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>9.59</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44854</v>
+        <v>44855</v>
       </c>
       <c r="H26" t="n">
-        <v>2199.05</v>
+        <v>2149.75</v>
       </c>
       <c r="I26" t="n">
         <v>2178.074237011533</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K26" t="n">
-        <v>-7.33</v>
+        <v>-9.41</v>
       </c>
       <c r="L26" t="n">
-        <v>7.79</v>
+        <v>10.24</v>
       </c>
       <c r="M26" t="n">
         <v>0.95</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>11.14</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44949</v>
+        <v>44950</v>
       </c>
       <c r="H27" t="n">
-        <v>1964.2</v>
+        <v>2043.05</v>
       </c>
       <c r="I27" t="n">
         <v>1971.645956290765</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K27" t="n">
-        <v>8.630000000000001</v>
+        <v>4.96</v>
       </c>
       <c r="L27" t="n">
         <v>3.75</v>
@@ -1980,7 +2303,7 @@
         <v>2.4</v>
       </c>
       <c r="N27" t="n">
-        <v>3.65</v>
+        <v>4.01</v>
       </c>
       <c r="O27" t="n">
         <v>-2.24</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>10.41</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44971</v>
+        <v>44972</v>
       </c>
       <c r="H28" t="n">
-        <v>1878.5</v>
+        <v>1856.75</v>
       </c>
       <c r="I28" t="n">
         <v>1864.229634519866</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K28" t="n">
-        <v>-8.050000000000001</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>9.06</v>
+        <v>9.52</v>
       </c>
       <c r="M28" t="n">
         <v>1.03</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>7.45</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44987</v>
+        <v>44988</v>
       </c>
       <c r="H29" t="n">
-        <v>1951.05</v>
+        <v>2003.5</v>
       </c>
       <c r="I29" t="n">
         <v>1994.192423427135</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K29" t="n">
-        <v>-5.08</v>
+        <v>-7.9</v>
       </c>
       <c r="L29" t="n">
-        <v>5.56</v>
+        <v>12.4</v>
       </c>
       <c r="M29" t="n">
         <v>1.24</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>7.12</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45005</v>
+        <v>45006</v>
       </c>
       <c r="H30" t="n">
-        <v>1898.4</v>
+        <v>1868.85</v>
       </c>
       <c r="I30" t="n">
         <v>1878.582403117376</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K30" t="n">
-        <v>-5.25</v>
+        <v>-6.72</v>
       </c>
       <c r="L30" t="n">
-        <v>6.36</v>
+        <v>6.91</v>
       </c>
       <c r="M30" t="n">
         <v>0.27</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>9.94</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45062</v>
+        <v>45063</v>
       </c>
       <c r="H31" t="n">
-        <v>1882.2</v>
+        <v>2171.85</v>
       </c>
       <c r="I31" t="n">
         <v>1925.092013774126</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.71</v>
+        <v>-16.21</v>
       </c>
       <c r="L31" t="n">
-        <v>4.23</v>
+        <v>19.27</v>
       </c>
       <c r="M31" t="n">
-        <v>1.17</v>
+        <v>15.29</v>
       </c>
       <c r="N31" t="n">
-        <v>2.02</v>
+        <v>15.39</v>
       </c>
       <c r="O31" t="n">
         <v>-1.56</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>11.42</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45331</v>
+        <v>45334</v>
       </c>
       <c r="H32" t="n">
-        <v>4157.65</v>
+        <v>3696.6</v>
       </c>
       <c r="I32" t="n">
         <v>3786.423112159626</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K32" t="n">
-        <v>91.43000000000001</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="L32" t="n">
         <v>7.3</v>
       </c>
       <c r="M32" t="n">
-        <v>4.83</v>
+        <v>11.01</v>
       </c>
       <c r="N32" t="n">
-        <v>7.99</v>
+        <v>11.09</v>
       </c>
       <c r="O32" t="n">
         <v>15.39</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>185</v>
+        <v>186</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>10</v>
+      </c>
+      <c r="U32" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>22.84</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="H33" t="n">
-        <v>3689.15</v>
+        <v>3764.6</v>
       </c>
       <c r="I33" t="n">
         <v>3693.863940467563</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2</v>
+        <v>-1.84</v>
       </c>
       <c r="L33" t="n">
         <v>12.21</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>13.04</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45439</v>
+        <v>45440</v>
       </c>
       <c r="H34" t="n">
-        <v>3733.1</v>
+        <v>3571.3</v>
       </c>
       <c r="I34" t="n">
         <v>3688.728405568486</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.84</v>
+        <v>-5.13</v>
       </c>
       <c r="L34" t="n">
         <v>6.95</v>
@@ -2379,7 +2786,7 @@
         <v>1.95</v>
       </c>
       <c r="N34" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="O34" t="n">
         <v>2.05</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>14.02</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45454</v>
+        <v>45455</v>
       </c>
       <c r="H35" t="n">
-        <v>3850.7</v>
+        <v>4077.4</v>
       </c>
       <c r="I35" t="n">
         <v>3947.761750025455</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K35" t="n">
-        <v>-7.82</v>
+        <v>-14.17</v>
       </c>
       <c r="L35" t="n">
-        <v>8.52</v>
+        <v>17.04</v>
       </c>
       <c r="M35" t="n">
         <v>4.06</v>
       </c>
       <c r="N35" t="n">
-        <v>3.44</v>
+        <v>5.89</v>
       </c>
       <c r="O35" t="n">
         <v>-4.33</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>13.93</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45491</v>
+        <v>45492</v>
       </c>
       <c r="H36" t="n">
-        <v>4428.65</v>
+        <v>4171.1</v>
       </c>
       <c r="I36" t="n">
         <v>4177.830650874797</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K36" t="n">
-        <v>8.609999999999999</v>
+        <v>2.3</v>
       </c>
       <c r="L36" t="n">
         <v>5.55</v>
@@ -2493,7 +2924,7 @@
         <v>0.33</v>
       </c>
       <c r="N36" t="n">
-        <v>3.58</v>
+        <v>5.82</v>
       </c>
       <c r="O36" t="n">
         <v>5.89</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>15.79</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H37" t="n">
-        <v>4510.85</v>
+        <v>4690.6</v>
       </c>
       <c r="I37" t="n">
         <v>4560.188375414138</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K37" t="n">
-        <v>-8.15</v>
+        <v>-12.45</v>
       </c>
       <c r="L37" t="n">
-        <v>10.64</v>
+        <v>13.16</v>
       </c>
       <c r="M37" t="n">
         <v>2.5</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>10.41</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45673</v>
+        <v>45674</v>
       </c>
       <c r="H38" t="n">
-        <v>6815.85</v>
+        <v>6757.5</v>
       </c>
       <c r="I38" t="n">
         <v>6762.123645655944</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K38" t="n">
-        <v>45.31</v>
+        <v>44.06</v>
       </c>
       <c r="L38" t="n">
         <v>9.050000000000001</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>5</v>
+      </c>
+      <c r="U38" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>19.6</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45734</v>
+        <v>45735</v>
       </c>
       <c r="H39" t="n">
-        <v>6632.85</v>
+        <v>6861.9</v>
       </c>
       <c r="I39" t="n">
         <v>6708.055450804881</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K39" t="n">
-        <v>1.84</v>
+        <v>-1.54</v>
       </c>
       <c r="L39" t="n">
         <v>8.01</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>15.12</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H40" t="n">
-        <v>6595.15</v>
+        <v>6151.4</v>
       </c>
       <c r="I40" t="n">
         <v>6298.766289722726</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>-3.89</v>
+        <v>-10.35</v>
       </c>
       <c r="L40" t="n">
-        <v>5.01</v>
+        <v>17.29</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8</v>
+        <v>13.57</v>
       </c>
       <c r="N40" t="n">
-        <v>4.94</v>
+        <v>6.73</v>
       </c>
       <c r="O40" t="n">
         <v>3.45</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>15.44</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45832</v>
+        <v>45833</v>
       </c>
       <c r="H41" t="n">
-        <v>6731</v>
+        <v>6836.5</v>
       </c>
       <c r="I41" t="n">
         <v>6734.23767378264</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K41" t="n">
-        <v>-9.42</v>
+        <v>-11.14</v>
       </c>
       <c r="L41" t="n">
         <v>13.37</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>9.93</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45877</v>
+        <v>45880</v>
       </c>
       <c r="H42" t="n">
-        <v>7354.5</v>
+        <v>6912.5</v>
       </c>
       <c r="I42" t="n">
         <v>7151.782265645232</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K42" t="n">
-        <v>7.58</v>
+        <v>1.11</v>
       </c>
       <c r="L42" t="n">
         <v>1.7</v>
@@ -2835,7 +3338,7 @@
         <v>1.44</v>
       </c>
       <c r="N42" t="n">
-        <v>4.85</v>
+        <v>6.01</v>
       </c>
       <c r="O42" t="n">
         <v>1.57</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>15.91</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45908</v>
+        <v>45909</v>
       </c>
       <c r="H43" t="n">
-        <v>7473</v>
+        <v>7817</v>
       </c>
       <c r="I43" t="n">
         <v>7801.682478428446</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K43" t="n">
-        <v>-8.109999999999999</v>
+        <v>-13.08</v>
       </c>
       <c r="L43" t="n">
         <v>14.26</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>13.09</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="H44" t="n">
-        <v>7957.5</v>
+        <v>7797.5</v>
       </c>
       <c r="I44" t="n">
         <v>7847.856148041464</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K44" t="n">
-        <v>1.8</v>
+        <v>-0.25</v>
       </c>
       <c r="L44" t="n">
         <v>5.64</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,25 +3524,25 @@
         <v>9.4</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="H45" t="n">
-        <v>5999</v>
+        <v>6193.5</v>
       </c>
       <c r="I45" t="n">
         <v>6069.35393049702</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K45" t="n">
-        <v>23.07</v>
+        <v>20.57</v>
       </c>
       <c r="L45" t="n">
         <v>2.5</v>
       </c>
       <c r="M45" t="n">
-        <v>1.29</v>
+        <v>5.02</v>
       </c>
       <c r="N45" t="n">
         <v>4.85</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H46" t="n">
-        <v>7872.5</v>
+        <v>7310.5</v>
       </c>
       <c r="I46" t="n">
         <v>7366.925831166202</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K46" t="n">
-        <v>27.11</v>
+        <v>18.04</v>
       </c>
       <c r="L46" t="n">
         <v>0.6899999999999999</v>
@@ -3063,7 +3614,7 @@
         <v>4.51</v>
       </c>
       <c r="N46" t="n">
-        <v>2.89</v>
+        <v>7.14</v>
       </c>
       <c r="O46" t="n">
         <v>3.24</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>14.42</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H47" t="n">
-        <v>6888.5</v>
+        <v>7245</v>
       </c>
       <c r="I47" t="n">
         <v>7214.07662287899</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K47" t="n">
-        <v>5.77</v>
+        <v>0.9</v>
       </c>
       <c r="L47" t="n">
         <v>6.28</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>15.24</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="H48" t="n">
-        <v>8476.5</v>
+        <v>7153.5</v>
       </c>
       <c r="I48" t="n">
         <v>7959.118240629029</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K48" t="n">
-        <v>17</v>
+        <v>-1.26</v>
       </c>
       <c r="L48" t="n">
         <v>3.76</v>
       </c>
       <c r="M48" t="n">
-        <v>3.11</v>
+        <v>4.23</v>
       </c>
       <c r="N48" t="n">
-        <v>4.4</v>
+        <v>15.61</v>
       </c>
       <c r="O48" t="n">
         <v>5.18</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>24.15</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="H49" t="n">
-        <v>7466</v>
+        <v>7701</v>
       </c>
       <c r="I49" t="n">
         <v>7649.364515171688</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.37</v>
+        <v>-7.65</v>
       </c>
       <c r="L49" t="n">
         <v>14.88</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>5</v>
+      </c>
+      <c r="U49" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>8.68</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H50" t="n">
-        <v>7245</v>
+        <v>7000</v>
       </c>
       <c r="I50" t="n">
         <v>7160.280912981061</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K50" t="n">
-        <v>-5.92</v>
+        <v>-9.1</v>
       </c>
       <c r="L50" t="n">
-        <v>7.47</v>
+        <v>9.92</v>
       </c>
       <c r="M50" t="n">
         <v>0.51</v>
       </c>
       <c r="N50" t="n">
-        <v>1.76</v>
+        <v>3.38</v>
       </c>
       <c r="O50" t="n">
         <v>3.15</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3351,6 +3962,14 @@
       <c r="Q51" t="n">
         <v>30</v>
       </c>
+      <c r="R51" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7085,7 +7704,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62.3</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6">
@@ -7095,7 +7714,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -7105,7 +7724,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="8">
@@ -7115,7 +7734,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -7125,7 +7744,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
@@ -7135,7 +7754,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>101.2</v>
+        <v>102.2</v>
       </c>
     </row>
     <row r="11">
@@ -7175,7 +7794,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8.08</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="15">
@@ -7185,7 +7804,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13.92</v>
+        <v>8.539999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -7195,7 +7814,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.99</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="17">
@@ -7205,7 +7824,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>137.37</v>
+        <v>124.33</v>
       </c>
     </row>
     <row r="18">
@@ -7215,7 +7834,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46.9</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="19">
@@ -7225,7 +7844,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.15</v>
+        <v>8.98</v>
       </c>
     </row>
     <row r="20">
@@ -7235,7 +7854,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.36</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -7245,7 +7864,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.88</v>
+        <v>19.27</v>
       </c>
     </row>
     <row r="22">
@@ -7255,7 +7874,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
@@ -7265,7 +7884,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -7275,7 +7894,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.5</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="25">
@@ -7285,7 +7904,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10.18</v>
+        <v>15.29</v>
       </c>
     </row>
     <row r="26">
@@ -7295,7 +7914,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.01</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="27">
@@ -7305,7 +7924,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.21</v>
+        <v>15.61</v>
       </c>
     </row>
     <row r="28">
@@ -7315,7 +7934,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29">
